--- a/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdFundDurationNew001_ls.xlsx
+++ b/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdFundDurationNew001_ls.xlsx
@@ -38,10 +38,6 @@
     <t>除权日</t>
   </si>
   <si>
-    <t>分红到账日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>红利再投日</t>
   </si>
   <si>
@@ -73,6 +69,10 @@
   </si>
   <si>
     <t>合作资产</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>红利下发日</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -471,16 +471,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -492,22 +492,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:16">
